--- a/target/classes/empleados.xlsx
+++ b/target/classes/empleados.xlsx
@@ -312,40 +312,40 @@
         <v>16</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>1592.17</v>
+        <v>1376.73</v>
       </c>
       <c r="E2" t="n" s="0">
-        <v>1382.41</v>
+        <v>1214.39</v>
       </c>
       <c r="F2" t="n" s="0">
-        <v>1895.58</v>
+        <v>1393.7</v>
       </c>
       <c r="G2" t="n" s="0">
-        <v>1554.53</v>
+        <v>1745.04</v>
       </c>
       <c r="H2" t="n" s="0">
-        <v>1470.84</v>
+        <v>1830.17</v>
       </c>
       <c r="I2" t="n" s="0">
-        <v>1562.3</v>
+        <v>1751.94</v>
       </c>
       <c r="J2" t="n" s="0">
-        <v>1469.66</v>
+        <v>1806.71</v>
       </c>
       <c r="K2" t="n" s="0">
-        <v>1387.97</v>
+        <v>1621.58</v>
       </c>
       <c r="L2" t="n" s="0">
-        <v>1901.68</v>
+        <v>1506.13</v>
       </c>
       <c r="M2" t="n" s="0">
-        <v>1772.27</v>
+        <v>1303.9</v>
       </c>
       <c r="N2" t="n" s="0">
-        <v>1297.87</v>
+        <v>1650.46</v>
       </c>
       <c r="O2" t="n" s="0">
-        <v>1787.81</v>
+        <v>1478.53</v>
       </c>
     </row>
     <row r="3">
@@ -359,40 +359,40 @@
         <v>18</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>1480.29</v>
+        <v>1986.6</v>
       </c>
       <c r="E3" t="n" s="0">
-        <v>1751.73</v>
+        <v>1790.81</v>
       </c>
       <c r="F3" t="n" s="0">
-        <v>1485.81</v>
+        <v>1871.87</v>
       </c>
       <c r="G3" t="n" s="0">
-        <v>1797.56</v>
+        <v>1688.56</v>
       </c>
       <c r="H3" t="n" s="0">
-        <v>1609.03</v>
+        <v>1777.74</v>
       </c>
       <c r="I3" t="n" s="0">
-        <v>1900.16</v>
+        <v>1579.99</v>
       </c>
       <c r="J3" t="n" s="0">
-        <v>1656.2</v>
+        <v>1404.27</v>
       </c>
       <c r="K3" t="n" s="0">
-        <v>1854.84</v>
+        <v>1973.59</v>
       </c>
       <c r="L3" t="n" s="0">
-        <v>1962.72</v>
+        <v>1257.08</v>
       </c>
       <c r="M3" t="n" s="0">
-        <v>1457.7</v>
+        <v>1873.28</v>
       </c>
       <c r="N3" t="n" s="0">
-        <v>1660.35</v>
+        <v>1533.89</v>
       </c>
       <c r="O3" t="n" s="0">
-        <v>1240.08</v>
+        <v>1818.2</v>
       </c>
     </row>
     <row r="4">
@@ -406,40 +406,40 @@
         <v>20</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>1437.28</v>
+        <v>1962.47</v>
       </c>
       <c r="E4" t="n" s="0">
-        <v>1605.77</v>
+        <v>1920.46</v>
       </c>
       <c r="F4" t="n" s="0">
-        <v>1978.1</v>
+        <v>1801.26</v>
       </c>
       <c r="G4" t="n" s="0">
-        <v>1252.25</v>
+        <v>1523.28</v>
       </c>
       <c r="H4" t="n" s="0">
-        <v>1576.88</v>
+        <v>1346.9</v>
       </c>
       <c r="I4" t="n" s="0">
-        <v>1781.5</v>
+        <v>1845.87</v>
       </c>
       <c r="J4" t="n" s="0">
-        <v>1674.01</v>
+        <v>1790.21</v>
       </c>
       <c r="K4" t="n" s="0">
-        <v>1392.83</v>
+        <v>1481.9</v>
       </c>
       <c r="L4" t="n" s="0">
-        <v>1875.92</v>
+        <v>1336.33</v>
       </c>
       <c r="M4" t="n" s="0">
-        <v>1581.17</v>
+        <v>1270.16</v>
       </c>
       <c r="N4" t="n" s="0">
-        <v>1590.88</v>
+        <v>1982.58</v>
       </c>
       <c r="O4" t="n" s="0">
-        <v>1833.94</v>
+        <v>1565.83</v>
       </c>
     </row>
     <row r="5">
@@ -453,40 +453,40 @@
         <v>22</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>1377.93</v>
+        <v>1666.48</v>
       </c>
       <c r="E5" t="n" s="0">
-        <v>1535.11</v>
+        <v>1328.92</v>
       </c>
       <c r="F5" t="n" s="0">
-        <v>1699.94</v>
+        <v>1908.08</v>
       </c>
       <c r="G5" t="n" s="0">
-        <v>1465.78</v>
+        <v>1243.59</v>
       </c>
       <c r="H5" t="n" s="0">
-        <v>1844.18</v>
+        <v>1837.1</v>
       </c>
       <c r="I5" t="n" s="0">
-        <v>1768.63</v>
+        <v>1534.26</v>
       </c>
       <c r="J5" t="n" s="0">
-        <v>1390.4</v>
+        <v>1893.93</v>
       </c>
       <c r="K5" t="n" s="0">
-        <v>1263.53</v>
+        <v>1407.78</v>
       </c>
       <c r="L5" t="n" s="0">
-        <v>1240.88</v>
+        <v>1411.15</v>
       </c>
       <c r="M5" t="n" s="0">
-        <v>1720.43</v>
+        <v>1594.85</v>
       </c>
       <c r="N5" t="n" s="0">
-        <v>1969.24</v>
+        <v>1820.1</v>
       </c>
       <c r="O5" t="n" s="0">
-        <v>1982.75</v>
+        <v>1271.39</v>
       </c>
     </row>
     <row r="6">
@@ -500,40 +500,40 @@
         <v>24</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>1994.13</v>
+        <v>1699.25</v>
       </c>
       <c r="E6" t="n" s="0">
-        <v>1872.05</v>
+        <v>1404.86</v>
       </c>
       <c r="F6" t="n" s="0">
-        <v>1355.45</v>
+        <v>1211.64</v>
       </c>
       <c r="G6" t="n" s="0">
-        <v>1687.6</v>
+        <v>1700.0</v>
       </c>
       <c r="H6" t="n" s="0">
-        <v>1988.02</v>
+        <v>1408.16</v>
       </c>
       <c r="I6" t="n" s="0">
-        <v>1448.85</v>
+        <v>1531.24</v>
       </c>
       <c r="J6" t="n" s="0">
-        <v>1891.24</v>
+        <v>1350.26</v>
       </c>
       <c r="K6" t="n" s="0">
-        <v>1934.96</v>
+        <v>1978.67</v>
       </c>
       <c r="L6" t="n" s="0">
-        <v>1231.88</v>
+        <v>1395.19</v>
       </c>
       <c r="M6" t="n" s="0">
-        <v>1485.32</v>
+        <v>1673.83</v>
       </c>
       <c r="N6" t="n" s="0">
-        <v>1755.93</v>
+        <v>1463.25</v>
       </c>
       <c r="O6" t="n" s="0">
-        <v>1582.79</v>
+        <v>1469.5</v>
       </c>
     </row>
     <row r="7">
@@ -547,40 +547,40 @@
         <v>26</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>1898.35</v>
+        <v>1259.13</v>
       </c>
       <c r="E7" t="n" s="0">
-        <v>1304.12</v>
+        <v>1341.86</v>
       </c>
       <c r="F7" t="n" s="0">
-        <v>1456.65</v>
+        <v>1848.62</v>
       </c>
       <c r="G7" t="n" s="0">
-        <v>1359.96</v>
+        <v>1297.55</v>
       </c>
       <c r="H7" t="n" s="0">
-        <v>1634.91</v>
+        <v>1510.85</v>
       </c>
       <c r="I7" t="n" s="0">
-        <v>1540.65</v>
+        <v>1385.29</v>
       </c>
       <c r="J7" t="n" s="0">
-        <v>1283.02</v>
+        <v>1820.84</v>
       </c>
       <c r="K7" t="n" s="0">
-        <v>1329.87</v>
+        <v>1710.4</v>
       </c>
       <c r="L7" t="n" s="0">
-        <v>1277.29</v>
+        <v>1905.91</v>
       </c>
       <c r="M7" t="n" s="0">
-        <v>1551.84</v>
+        <v>1438.77</v>
       </c>
       <c r="N7" t="n" s="0">
-        <v>1451.68</v>
+        <v>1612.84</v>
       </c>
       <c r="O7" t="n" s="0">
-        <v>1599.17</v>
+        <v>1687.97</v>
       </c>
     </row>
     <row r="8">
@@ -594,40 +594,40 @@
         <v>28</v>
       </c>
       <c r="D8" t="n" s="0">
-        <v>1943.64</v>
+        <v>1983.88</v>
       </c>
       <c r="E8" t="n" s="0">
-        <v>1779.89</v>
+        <v>1980.6</v>
       </c>
       <c r="F8" t="n" s="0">
-        <v>1529.29</v>
+        <v>1645.17</v>
       </c>
       <c r="G8" t="n" s="0">
-        <v>1267.99</v>
+        <v>1536.93</v>
       </c>
       <c r="H8" t="n" s="0">
-        <v>1764.7</v>
+        <v>1548.1</v>
       </c>
       <c r="I8" t="n" s="0">
-        <v>1998.59</v>
+        <v>1778.58</v>
       </c>
       <c r="J8" t="n" s="0">
-        <v>1611.31</v>
+        <v>1474.47</v>
       </c>
       <c r="K8" t="n" s="0">
-        <v>1287.07</v>
+        <v>1785.51</v>
       </c>
       <c r="L8" t="n" s="0">
-        <v>1605.38</v>
+        <v>1932.48</v>
       </c>
       <c r="M8" t="n" s="0">
-        <v>1952.24</v>
+        <v>1589.19</v>
       </c>
       <c r="N8" t="n" s="0">
-        <v>1847.08</v>
+        <v>1458.79</v>
       </c>
       <c r="O8" t="n" s="0">
-        <v>1582.15</v>
+        <v>1901.86</v>
       </c>
     </row>
     <row r="9">
@@ -641,40 +641,40 @@
         <v>30</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>1659.35</v>
+        <v>1840.26</v>
       </c>
       <c r="E9" t="n" s="0">
-        <v>1703.8</v>
+        <v>1496.07</v>
       </c>
       <c r="F9" t="n" s="0">
-        <v>1639.73</v>
+        <v>1928.39</v>
       </c>
       <c r="G9" t="n" s="0">
-        <v>1525.24</v>
+        <v>1391.09</v>
       </c>
       <c r="H9" t="n" s="0">
-        <v>1548.89</v>
+        <v>1903.11</v>
       </c>
       <c r="I9" t="n" s="0">
-        <v>1841.17</v>
+        <v>1818.24</v>
       </c>
       <c r="J9" t="n" s="0">
-        <v>1613.15</v>
+        <v>1426.23</v>
       </c>
       <c r="K9" t="n" s="0">
-        <v>1577.04</v>
+        <v>1683.15</v>
       </c>
       <c r="L9" t="n" s="0">
-        <v>1537.96</v>
+        <v>1497.03</v>
       </c>
       <c r="M9" t="n" s="0">
-        <v>1747.59</v>
+        <v>1288.21</v>
       </c>
       <c r="N9" t="n" s="0">
-        <v>1426.19</v>
+        <v>1383.27</v>
       </c>
       <c r="O9" t="n" s="0">
-        <v>1894.31</v>
+        <v>1505.55</v>
       </c>
     </row>
     <row r="10">
@@ -688,40 +688,40 @@
         <v>32</v>
       </c>
       <c r="D10" t="n" s="0">
-        <v>1667.44</v>
+        <v>1764.97</v>
       </c>
       <c r="E10" t="n" s="0">
-        <v>1823.86</v>
+        <v>1594.33</v>
       </c>
       <c r="F10" t="n" s="0">
-        <v>1527.72</v>
+        <v>1419.36</v>
       </c>
       <c r="G10" t="n" s="0">
-        <v>1690.43</v>
+        <v>1542.34</v>
       </c>
       <c r="H10" t="n" s="0">
-        <v>1846.95</v>
+        <v>1834.18</v>
       </c>
       <c r="I10" t="n" s="0">
-        <v>1657.6</v>
+        <v>1601.74</v>
       </c>
       <c r="J10" t="n" s="0">
-        <v>1784.36</v>
+        <v>1311.4</v>
       </c>
       <c r="K10" t="n" s="0">
-        <v>1957.02</v>
+        <v>1312.41</v>
       </c>
       <c r="L10" t="n" s="0">
-        <v>1588.78</v>
+        <v>1279.72</v>
       </c>
       <c r="M10" t="n" s="0">
-        <v>1866.23</v>
+        <v>1610.25</v>
       </c>
       <c r="N10" t="n" s="0">
-        <v>1376.11</v>
+        <v>1346.14</v>
       </c>
       <c r="O10" t="n" s="0">
-        <v>1399.09</v>
+        <v>1557.44</v>
       </c>
     </row>
     <row r="11">
@@ -735,40 +735,40 @@
         <v>34</v>
       </c>
       <c r="D11" t="n" s="0">
-        <v>1545.04</v>
+        <v>1773.86</v>
       </c>
       <c r="E11" t="n" s="0">
-        <v>1897.99</v>
+        <v>1877.51</v>
       </c>
       <c r="F11" t="n" s="0">
-        <v>1643.22</v>
+        <v>1875.85</v>
       </c>
       <c r="G11" t="n" s="0">
-        <v>1505.39</v>
+        <v>1411.8</v>
       </c>
       <c r="H11" t="n" s="0">
-        <v>1909.9</v>
+        <v>1774.22</v>
       </c>
       <c r="I11" t="n" s="0">
-        <v>1856.72</v>
+        <v>1530.07</v>
       </c>
       <c r="J11" t="n" s="0">
-        <v>1481.02</v>
+        <v>1420.77</v>
       </c>
       <c r="K11" t="n" s="0">
-        <v>1570.61</v>
+        <v>1233.67</v>
       </c>
       <c r="L11" t="n" s="0">
-        <v>1474.78</v>
+        <v>1641.98</v>
       </c>
       <c r="M11" t="n" s="0">
-        <v>1823.75</v>
+        <v>1504.52</v>
       </c>
       <c r="N11" t="n" s="0">
-        <v>1417.76</v>
+        <v>1413.16</v>
       </c>
       <c r="O11" t="n" s="0">
-        <v>1805.28</v>
+        <v>1208.77</v>
       </c>
     </row>
     <row r="12">
@@ -782,40 +782,40 @@
         <v>36</v>
       </c>
       <c r="D12" t="n" s="0">
-        <v>1674.84</v>
+        <v>1944.63</v>
       </c>
       <c r="E12" t="n" s="0">
-        <v>1581.85</v>
+        <v>1905.55</v>
       </c>
       <c r="F12" t="n" s="0">
-        <v>1673.61</v>
+        <v>1453.45</v>
       </c>
       <c r="G12" t="n" s="0">
-        <v>1613.92</v>
+        <v>1895.11</v>
       </c>
       <c r="H12" t="n" s="0">
-        <v>1941.18</v>
+        <v>1686.03</v>
       </c>
       <c r="I12" t="n" s="0">
-        <v>1903.36</v>
+        <v>1737.01</v>
       </c>
       <c r="J12" t="n" s="0">
-        <v>1687.49</v>
+        <v>1349.73</v>
       </c>
       <c r="K12" t="n" s="0">
-        <v>1491.36</v>
+        <v>1759.06</v>
       </c>
       <c r="L12" t="n" s="0">
-        <v>1673.68</v>
+        <v>1819.95</v>
       </c>
       <c r="M12" t="n" s="0">
-        <v>1246.81</v>
+        <v>1357.08</v>
       </c>
       <c r="N12" t="n" s="0">
-        <v>1411.51</v>
+        <v>1637.85</v>
       </c>
       <c r="O12" t="n" s="0">
-        <v>1981.97</v>
+        <v>1260.37</v>
       </c>
     </row>
     <row r="13">
@@ -829,40 +829,40 @@
         <v>38</v>
       </c>
       <c r="D13" t="n" s="0">
-        <v>1775.51</v>
+        <v>1441.35</v>
       </c>
       <c r="E13" t="n" s="0">
-        <v>1613.02</v>
+        <v>1627.54</v>
       </c>
       <c r="F13" t="n" s="0">
-        <v>1711.02</v>
+        <v>1529.84</v>
       </c>
       <c r="G13" t="n" s="0">
-        <v>1765.65</v>
+        <v>1575.42</v>
       </c>
       <c r="H13" t="n" s="0">
-        <v>1740.73</v>
+        <v>1913.09</v>
       </c>
       <c r="I13" t="n" s="0">
-        <v>1244.13</v>
+        <v>1372.27</v>
       </c>
       <c r="J13" t="n" s="0">
-        <v>1671.91</v>
+        <v>1914.38</v>
       </c>
       <c r="K13" t="n" s="0">
-        <v>1979.44</v>
+        <v>1405.4</v>
       </c>
       <c r="L13" t="n" s="0">
-        <v>1562.51</v>
+        <v>1474.02</v>
       </c>
       <c r="M13" t="n" s="0">
-        <v>1405.57</v>
+        <v>1229.29</v>
       </c>
       <c r="N13" t="n" s="0">
-        <v>1704.61</v>
+        <v>1533.74</v>
       </c>
       <c r="O13" t="n" s="0">
-        <v>1352.72</v>
+        <v>1897.75</v>
       </c>
     </row>
     <row r="14">
@@ -876,40 +876,40 @@
         <v>40</v>
       </c>
       <c r="D14" t="n" s="0">
-        <v>1230.16</v>
+        <v>1587.59</v>
       </c>
       <c r="E14" t="n" s="0">
-        <v>1673.56</v>
+        <v>1675.22</v>
       </c>
       <c r="F14" t="n" s="0">
-        <v>1447.78</v>
+        <v>1987.44</v>
       </c>
       <c r="G14" t="n" s="0">
-        <v>1428.75</v>
+        <v>1916.65</v>
       </c>
       <c r="H14" t="n" s="0">
-        <v>1908.92</v>
+        <v>1228.49</v>
       </c>
       <c r="I14" t="n" s="0">
-        <v>1357.13</v>
+        <v>1520.68</v>
       </c>
       <c r="J14" t="n" s="0">
-        <v>1813.1</v>
+        <v>1363.61</v>
       </c>
       <c r="K14" t="n" s="0">
-        <v>1864.76</v>
+        <v>1329.98</v>
       </c>
       <c r="L14" t="n" s="0">
-        <v>1647.16</v>
+        <v>1668.17</v>
       </c>
       <c r="M14" t="n" s="0">
-        <v>1516.3</v>
+        <v>1319.7</v>
       </c>
       <c r="N14" t="n" s="0">
-        <v>1875.38</v>
+        <v>1874.76</v>
       </c>
       <c r="O14" t="n" s="0">
-        <v>1347.39</v>
+        <v>1437.53</v>
       </c>
     </row>
     <row r="15">
@@ -923,40 +923,40 @@
         <v>42</v>
       </c>
       <c r="D15" t="n" s="0">
-        <v>1431.75</v>
+        <v>1308.07</v>
       </c>
       <c r="E15" t="n" s="0">
-        <v>1294.66</v>
+        <v>1905.42</v>
       </c>
       <c r="F15" t="n" s="0">
-        <v>1301.12</v>
+        <v>1475.72</v>
       </c>
       <c r="G15" t="n" s="0">
-        <v>1229.56</v>
+        <v>1546.99</v>
       </c>
       <c r="H15" t="n" s="0">
-        <v>1812.67</v>
+        <v>1323.2</v>
       </c>
       <c r="I15" t="n" s="0">
-        <v>1566.71</v>
+        <v>1659.41</v>
       </c>
       <c r="J15" t="n" s="0">
-        <v>1621.25</v>
+        <v>1466.88</v>
       </c>
       <c r="K15" t="n" s="0">
-        <v>1389.86</v>
+        <v>1411.52</v>
       </c>
       <c r="L15" t="n" s="0">
-        <v>1744.13</v>
+        <v>1916.38</v>
       </c>
       <c r="M15" t="n" s="0">
-        <v>1807.61</v>
+        <v>1941.08</v>
       </c>
       <c r="N15" t="n" s="0">
-        <v>1692.79</v>
+        <v>1536.92</v>
       </c>
       <c r="O15" t="n" s="0">
-        <v>1834.52</v>
+        <v>1974.6</v>
       </c>
     </row>
     <row r="16">
@@ -970,40 +970,40 @@
         <v>44</v>
       </c>
       <c r="D16" t="n" s="0">
-        <v>1739.96</v>
+        <v>1847.23</v>
       </c>
       <c r="E16" t="n" s="0">
-        <v>1824.59</v>
+        <v>1948.23</v>
       </c>
       <c r="F16" t="n" s="0">
-        <v>1756.7</v>
+        <v>1775.06</v>
       </c>
       <c r="G16" t="n" s="0">
-        <v>1607.08</v>
+        <v>1224.85</v>
       </c>
       <c r="H16" t="n" s="0">
-        <v>1317.04</v>
+        <v>1387.98</v>
       </c>
       <c r="I16" t="n" s="0">
-        <v>1746.67</v>
+        <v>1349.49</v>
       </c>
       <c r="J16" t="n" s="0">
-        <v>1788.1</v>
+        <v>1483.37</v>
       </c>
       <c r="K16" t="n" s="0">
-        <v>1839.91</v>
+        <v>1545.77</v>
       </c>
       <c r="L16" t="n" s="0">
-        <v>1201.06</v>
+        <v>1371.64</v>
       </c>
       <c r="M16" t="n" s="0">
-        <v>1851.21</v>
+        <v>1723.82</v>
       </c>
       <c r="N16" t="n" s="0">
-        <v>1747.98</v>
+        <v>1945.59</v>
       </c>
       <c r="O16" t="n" s="0">
-        <v>1876.73</v>
+        <v>1352.01</v>
       </c>
     </row>
     <row r="17">
@@ -1017,40 +1017,40 @@
         <v>46</v>
       </c>
       <c r="D17" t="n" s="0">
-        <v>1895.0</v>
+        <v>1336.15</v>
       </c>
       <c r="E17" t="n" s="0">
-        <v>1612.81</v>
+        <v>1361.74</v>
       </c>
       <c r="F17" t="n" s="0">
-        <v>1483.89</v>
+        <v>1459.94</v>
       </c>
       <c r="G17" t="n" s="0">
-        <v>1514.42</v>
+        <v>1836.2</v>
       </c>
       <c r="H17" t="n" s="0">
-        <v>1561.19</v>
+        <v>1531.66</v>
       </c>
       <c r="I17" t="n" s="0">
-        <v>1592.19</v>
+        <v>1927.56</v>
       </c>
       <c r="J17" t="n" s="0">
-        <v>1990.31</v>
+        <v>1518.64</v>
       </c>
       <c r="K17" t="n" s="0">
-        <v>1357.3</v>
+        <v>1707.15</v>
       </c>
       <c r="L17" t="n" s="0">
-        <v>1743.82</v>
+        <v>1946.1</v>
       </c>
       <c r="M17" t="n" s="0">
-        <v>1639.75</v>
+        <v>1851.34</v>
       </c>
       <c r="N17" t="n" s="0">
-        <v>1927.87</v>
+        <v>1418.19</v>
       </c>
       <c r="O17" t="n" s="0">
-        <v>1446.14</v>
+        <v>1282.31</v>
       </c>
     </row>
     <row r="18">
@@ -1064,40 +1064,40 @@
         <v>48</v>
       </c>
       <c r="D18" t="n" s="0">
-        <v>1259.41</v>
+        <v>1717.76</v>
       </c>
       <c r="E18" t="n" s="0">
-        <v>1970.32</v>
+        <v>1714.0</v>
       </c>
       <c r="F18" t="n" s="0">
-        <v>1313.7</v>
+        <v>1609.91</v>
       </c>
       <c r="G18" t="n" s="0">
-        <v>1319.26</v>
+        <v>1804.52</v>
       </c>
       <c r="H18" t="n" s="0">
-        <v>1408.6</v>
+        <v>1541.62</v>
       </c>
       <c r="I18" t="n" s="0">
-        <v>1972.96</v>
+        <v>1708.27</v>
       </c>
       <c r="J18" t="n" s="0">
-        <v>1733.45</v>
+        <v>1351.08</v>
       </c>
       <c r="K18" t="n" s="0">
-        <v>1682.09</v>
+        <v>1584.9</v>
       </c>
       <c r="L18" t="n" s="0">
-        <v>1913.43</v>
+        <v>1539.64</v>
       </c>
       <c r="M18" t="n" s="0">
-        <v>1551.47</v>
+        <v>1702.95</v>
       </c>
       <c r="N18" t="n" s="0">
-        <v>1288.98</v>
+        <v>1293.0</v>
       </c>
       <c r="O18" t="n" s="0">
-        <v>1306.33</v>
+        <v>1531.06</v>
       </c>
     </row>
     <row r="19">
@@ -1111,40 +1111,40 @@
         <v>50</v>
       </c>
       <c r="D19" t="n" s="0">
-        <v>1459.96</v>
+        <v>1953.39</v>
       </c>
       <c r="E19" t="n" s="0">
-        <v>1348.3</v>
+        <v>1307.34</v>
       </c>
       <c r="F19" t="n" s="0">
-        <v>1983.81</v>
+        <v>1742.65</v>
       </c>
       <c r="G19" t="n" s="0">
-        <v>1449.5</v>
+        <v>1201.47</v>
       </c>
       <c r="H19" t="n" s="0">
-        <v>1426.91</v>
+        <v>1930.81</v>
       </c>
       <c r="I19" t="n" s="0">
-        <v>1786.79</v>
+        <v>1427.28</v>
       </c>
       <c r="J19" t="n" s="0">
-        <v>1361.88</v>
+        <v>1660.88</v>
       </c>
       <c r="K19" t="n" s="0">
-        <v>1979.92</v>
+        <v>1534.28</v>
       </c>
       <c r="L19" t="n" s="0">
-        <v>1506.86</v>
+        <v>1416.96</v>
       </c>
       <c r="M19" t="n" s="0">
-        <v>1273.44</v>
+        <v>1323.77</v>
       </c>
       <c r="N19" t="n" s="0">
-        <v>1753.17</v>
+        <v>1610.63</v>
       </c>
       <c r="O19" t="n" s="0">
-        <v>1711.85</v>
+        <v>1430.45</v>
       </c>
     </row>
     <row r="20">
@@ -1158,40 +1158,40 @@
         <v>52</v>
       </c>
       <c r="D20" t="n" s="0">
-        <v>1877.2</v>
+        <v>1922.08</v>
       </c>
       <c r="E20" t="n" s="0">
-        <v>1534.15</v>
+        <v>1329.64</v>
       </c>
       <c r="F20" t="n" s="0">
-        <v>1843.47</v>
+        <v>1444.26</v>
       </c>
       <c r="G20" t="n" s="0">
-        <v>1800.11</v>
+        <v>1628.57</v>
       </c>
       <c r="H20" t="n" s="0">
-        <v>1953.89</v>
+        <v>1728.64</v>
       </c>
       <c r="I20" t="n" s="0">
-        <v>1315.24</v>
+        <v>1949.3</v>
       </c>
       <c r="J20" t="n" s="0">
-        <v>1273.34</v>
+        <v>1320.31</v>
       </c>
       <c r="K20" t="n" s="0">
-        <v>1812.86</v>
+        <v>1990.34</v>
       </c>
       <c r="L20" t="n" s="0">
-        <v>1761.81</v>
+        <v>1911.88</v>
       </c>
       <c r="M20" t="n" s="0">
-        <v>1762.18</v>
+        <v>1461.17</v>
       </c>
       <c r="N20" t="n" s="0">
-        <v>1585.0</v>
+        <v>1865.33</v>
       </c>
       <c r="O20" t="n" s="0">
-        <v>1295.94</v>
+        <v>1423.0</v>
       </c>
     </row>
     <row r="21">
@@ -1205,40 +1205,40 @@
         <v>54</v>
       </c>
       <c r="D21" t="n" s="0">
-        <v>1381.33</v>
+        <v>1387.39</v>
       </c>
       <c r="E21" t="n" s="0">
-        <v>1696.09</v>
+        <v>1961.79</v>
       </c>
       <c r="F21" t="n" s="0">
-        <v>1273.92</v>
+        <v>1547.55</v>
       </c>
       <c r="G21" t="n" s="0">
-        <v>1661.53</v>
+        <v>1596.95</v>
       </c>
       <c r="H21" t="n" s="0">
-        <v>1581.51</v>
+        <v>1261.67</v>
       </c>
       <c r="I21" t="n" s="0">
-        <v>1539.76</v>
+        <v>1235.34</v>
       </c>
       <c r="J21" t="n" s="0">
-        <v>1365.31</v>
+        <v>1804.7</v>
       </c>
       <c r="K21" t="n" s="0">
-        <v>1678.51</v>
+        <v>1973.77</v>
       </c>
       <c r="L21" t="n" s="0">
-        <v>1825.98</v>
+        <v>1850.76</v>
       </c>
       <c r="M21" t="n" s="0">
-        <v>1602.45</v>
+        <v>1301.56</v>
       </c>
       <c r="N21" t="n" s="0">
-        <v>1623.94</v>
+        <v>1969.26</v>
       </c>
       <c r="O21" t="n" s="0">
-        <v>1911.45</v>
+        <v>1641.92</v>
       </c>
     </row>
     <row r="22">
@@ -1252,40 +1252,40 @@
         <v>56</v>
       </c>
       <c r="D22" t="n" s="0">
-        <v>1538.5</v>
+        <v>1444.53</v>
       </c>
       <c r="E22" t="n" s="0">
-        <v>1814.34</v>
+        <v>1590.0</v>
       </c>
       <c r="F22" t="n" s="0">
-        <v>1818.9</v>
+        <v>1359.93</v>
       </c>
       <c r="G22" t="n" s="0">
-        <v>1549.67</v>
+        <v>1864.54</v>
       </c>
       <c r="H22" t="n" s="0">
-        <v>1641.02</v>
+        <v>1433.14</v>
       </c>
       <c r="I22" t="n" s="0">
-        <v>1808.71</v>
+        <v>1407.5</v>
       </c>
       <c r="J22" t="n" s="0">
-        <v>1803.38</v>
+        <v>1859.38</v>
       </c>
       <c r="K22" t="n" s="0">
-        <v>1987.28</v>
+        <v>1675.53</v>
       </c>
       <c r="L22" t="n" s="0">
-        <v>1527.46</v>
+        <v>1375.03</v>
       </c>
       <c r="M22" t="n" s="0">
-        <v>1682.08</v>
+        <v>1510.91</v>
       </c>
       <c r="N22" t="n" s="0">
-        <v>1732.77</v>
+        <v>1673.47</v>
       </c>
       <c r="O22" t="n" s="0">
-        <v>1259.72</v>
+        <v>1317.54</v>
       </c>
     </row>
     <row r="23">
@@ -1299,40 +1299,40 @@
         <v>58</v>
       </c>
       <c r="D23" t="n" s="0">
-        <v>1412.89</v>
+        <v>1974.29</v>
       </c>
       <c r="E23" t="n" s="0">
-        <v>1219.32</v>
+        <v>1766.16</v>
       </c>
       <c r="F23" t="n" s="0">
-        <v>1932.43</v>
+        <v>1768.51</v>
       </c>
       <c r="G23" t="n" s="0">
-        <v>1611.83</v>
+        <v>1996.98</v>
       </c>
       <c r="H23" t="n" s="0">
-        <v>1797.78</v>
+        <v>1348.52</v>
       </c>
       <c r="I23" t="n" s="0">
-        <v>1652.93</v>
+        <v>1869.62</v>
       </c>
       <c r="J23" t="n" s="0">
-        <v>1940.25</v>
+        <v>1908.49</v>
       </c>
       <c r="K23" t="n" s="0">
-        <v>1467.02</v>
+        <v>1738.8</v>
       </c>
       <c r="L23" t="n" s="0">
-        <v>1413.43</v>
+        <v>1606.45</v>
       </c>
       <c r="M23" t="n" s="0">
-        <v>1932.66</v>
+        <v>1726.89</v>
       </c>
       <c r="N23" t="n" s="0">
-        <v>1686.82</v>
+        <v>1665.28</v>
       </c>
       <c r="O23" t="n" s="0">
-        <v>1286.57</v>
+        <v>1655.3</v>
       </c>
     </row>
     <row r="24">
@@ -1346,40 +1346,40 @@
         <v>60</v>
       </c>
       <c r="D24" t="n" s="0">
-        <v>1265.09</v>
+        <v>1818.02</v>
       </c>
       <c r="E24" t="n" s="0">
-        <v>1413.83</v>
+        <v>1729.13</v>
       </c>
       <c r="F24" t="n" s="0">
-        <v>1839.84</v>
+        <v>1650.38</v>
       </c>
       <c r="G24" t="n" s="0">
-        <v>1852.77</v>
+        <v>1900.53</v>
       </c>
       <c r="H24" t="n" s="0">
-        <v>1265.24</v>
+        <v>1547.94</v>
       </c>
       <c r="I24" t="n" s="0">
-        <v>1629.38</v>
+        <v>1636.14</v>
       </c>
       <c r="J24" t="n" s="0">
-        <v>1827.24</v>
+        <v>1517.65</v>
       </c>
       <c r="K24" t="n" s="0">
-        <v>1378.93</v>
+        <v>1963.95</v>
       </c>
       <c r="L24" t="n" s="0">
-        <v>1850.14</v>
+        <v>1836.69</v>
       </c>
       <c r="M24" t="n" s="0">
-        <v>1393.15</v>
+        <v>1270.2</v>
       </c>
       <c r="N24" t="n" s="0">
-        <v>1367.19</v>
+        <v>1212.32</v>
       </c>
       <c r="O24" t="n" s="0">
-        <v>1344.06</v>
+        <v>1763.71</v>
       </c>
     </row>
     <row r="25">
@@ -1393,40 +1393,40 @@
         <v>62</v>
       </c>
       <c r="D25" t="n" s="0">
-        <v>1498.67</v>
+        <v>1451.67</v>
       </c>
       <c r="E25" t="n" s="0">
-        <v>1888.61</v>
+        <v>1544.13</v>
       </c>
       <c r="F25" t="n" s="0">
-        <v>1270.96</v>
+        <v>1692.18</v>
       </c>
       <c r="G25" t="n" s="0">
-        <v>1269.35</v>
+        <v>1832.3</v>
       </c>
       <c r="H25" t="n" s="0">
-        <v>1823.23</v>
+        <v>1394.18</v>
       </c>
       <c r="I25" t="n" s="0">
-        <v>1629.41</v>
+        <v>1691.58</v>
       </c>
       <c r="J25" t="n" s="0">
-        <v>1448.45</v>
+        <v>1322.85</v>
       </c>
       <c r="K25" t="n" s="0">
-        <v>1398.22</v>
+        <v>1944.2</v>
       </c>
       <c r="L25" t="n" s="0">
-        <v>1278.2</v>
+        <v>1236.3</v>
       </c>
       <c r="M25" t="n" s="0">
-        <v>1235.1</v>
+        <v>1536.95</v>
       </c>
       <c r="N25" t="n" s="0">
-        <v>1233.89</v>
+        <v>1549.52</v>
       </c>
       <c r="O25" t="n" s="0">
-        <v>1811.26</v>
+        <v>1817.04</v>
       </c>
     </row>
     <row r="26">
@@ -1440,40 +1440,40 @@
         <v>64</v>
       </c>
       <c r="D26" t="n" s="0">
-        <v>1332.26</v>
+        <v>1674.9</v>
       </c>
       <c r="E26" t="n" s="0">
-        <v>1247.55</v>
+        <v>1437.23</v>
       </c>
       <c r="F26" t="n" s="0">
-        <v>1763.02</v>
+        <v>1473.72</v>
       </c>
       <c r="G26" t="n" s="0">
-        <v>1301.75</v>
+        <v>1425.28</v>
       </c>
       <c r="H26" t="n" s="0">
-        <v>1976.7</v>
+        <v>1928.58</v>
       </c>
       <c r="I26" t="n" s="0">
-        <v>1920.34</v>
+        <v>1547.13</v>
       </c>
       <c r="J26" t="n" s="0">
-        <v>1771.01</v>
+        <v>1214.07</v>
       </c>
       <c r="K26" t="n" s="0">
-        <v>1757.22</v>
+        <v>1996.71</v>
       </c>
       <c r="L26" t="n" s="0">
-        <v>1892.57</v>
+        <v>1466.26</v>
       </c>
       <c r="M26" t="n" s="0">
-        <v>1245.76</v>
+        <v>1903.68</v>
       </c>
       <c r="N26" t="n" s="0">
-        <v>1243.78</v>
+        <v>1205.99</v>
       </c>
       <c r="O26" t="n" s="0">
-        <v>1836.86</v>
+        <v>1919.94</v>
       </c>
     </row>
   </sheetData>

--- a/target/classes/empleados.xlsx
+++ b/target/classes/empleados.xlsx
@@ -312,40 +312,40 @@
         <v>16</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>1376.73</v>
+        <v>1663.65</v>
       </c>
       <c r="E2" t="n" s="0">
-        <v>1214.39</v>
+        <v>1340.05</v>
       </c>
       <c r="F2" t="n" s="0">
-        <v>1393.7</v>
+        <v>1448.85</v>
       </c>
       <c r="G2" t="n" s="0">
-        <v>1745.04</v>
+        <v>1456.37</v>
       </c>
       <c r="H2" t="n" s="0">
-        <v>1830.17</v>
+        <v>1437.02</v>
       </c>
       <c r="I2" t="n" s="0">
-        <v>1751.94</v>
+        <v>1526.03</v>
       </c>
       <c r="J2" t="n" s="0">
-        <v>1806.71</v>
+        <v>1730.26</v>
       </c>
       <c r="K2" t="n" s="0">
-        <v>1621.58</v>
+        <v>1856.07</v>
       </c>
       <c r="L2" t="n" s="0">
-        <v>1506.13</v>
+        <v>1600.09</v>
       </c>
       <c r="M2" t="n" s="0">
-        <v>1303.9</v>
+        <v>1427.48</v>
       </c>
       <c r="N2" t="n" s="0">
-        <v>1650.46</v>
+        <v>1707.35</v>
       </c>
       <c r="O2" t="n" s="0">
-        <v>1478.53</v>
+        <v>1463.48</v>
       </c>
     </row>
     <row r="3">
@@ -359,40 +359,40 @@
         <v>18</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>1986.6</v>
+        <v>1378.58</v>
       </c>
       <c r="E3" t="n" s="0">
-        <v>1790.81</v>
+        <v>1367.07</v>
       </c>
       <c r="F3" t="n" s="0">
-        <v>1871.87</v>
+        <v>1394.02</v>
       </c>
       <c r="G3" t="n" s="0">
-        <v>1688.56</v>
+        <v>1574.44</v>
       </c>
       <c r="H3" t="n" s="0">
-        <v>1777.74</v>
+        <v>1963.58</v>
       </c>
       <c r="I3" t="n" s="0">
-        <v>1579.99</v>
+        <v>1283.82</v>
       </c>
       <c r="J3" t="n" s="0">
-        <v>1404.27</v>
+        <v>1765.06</v>
       </c>
       <c r="K3" t="n" s="0">
-        <v>1973.59</v>
+        <v>1502.09</v>
       </c>
       <c r="L3" t="n" s="0">
-        <v>1257.08</v>
+        <v>1506.6</v>
       </c>
       <c r="M3" t="n" s="0">
-        <v>1873.28</v>
+        <v>1597.76</v>
       </c>
       <c r="N3" t="n" s="0">
-        <v>1533.89</v>
+        <v>1278.7</v>
       </c>
       <c r="O3" t="n" s="0">
-        <v>1818.2</v>
+        <v>1265.75</v>
       </c>
     </row>
     <row r="4">
@@ -406,40 +406,40 @@
         <v>20</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>1962.47</v>
+        <v>1218.67</v>
       </c>
       <c r="E4" t="n" s="0">
-        <v>1920.46</v>
+        <v>1716.94</v>
       </c>
       <c r="F4" t="n" s="0">
-        <v>1801.26</v>
+        <v>1972.42</v>
       </c>
       <c r="G4" t="n" s="0">
-        <v>1523.28</v>
+        <v>1934.97</v>
       </c>
       <c r="H4" t="n" s="0">
-        <v>1346.9</v>
+        <v>1568.46</v>
       </c>
       <c r="I4" t="n" s="0">
-        <v>1845.87</v>
+        <v>1439.11</v>
       </c>
       <c r="J4" t="n" s="0">
-        <v>1790.21</v>
+        <v>1893.29</v>
       </c>
       <c r="K4" t="n" s="0">
-        <v>1481.9</v>
+        <v>1712.7</v>
       </c>
       <c r="L4" t="n" s="0">
-        <v>1336.33</v>
+        <v>1662.93</v>
       </c>
       <c r="M4" t="n" s="0">
-        <v>1270.16</v>
+        <v>1369.98</v>
       </c>
       <c r="N4" t="n" s="0">
-        <v>1982.58</v>
+        <v>1924.6</v>
       </c>
       <c r="O4" t="n" s="0">
-        <v>1565.83</v>
+        <v>1623.64</v>
       </c>
     </row>
     <row r="5">
@@ -453,40 +453,40 @@
         <v>22</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>1666.48</v>
+        <v>1207.24</v>
       </c>
       <c r="E5" t="n" s="0">
-        <v>1328.92</v>
+        <v>1774.49</v>
       </c>
       <c r="F5" t="n" s="0">
-        <v>1908.08</v>
+        <v>1396.74</v>
       </c>
       <c r="G5" t="n" s="0">
-        <v>1243.59</v>
+        <v>1680.75</v>
       </c>
       <c r="H5" t="n" s="0">
-        <v>1837.1</v>
+        <v>1378.84</v>
       </c>
       <c r="I5" t="n" s="0">
-        <v>1534.26</v>
+        <v>1397.11</v>
       </c>
       <c r="J5" t="n" s="0">
-        <v>1893.93</v>
+        <v>1420.59</v>
       </c>
       <c r="K5" t="n" s="0">
-        <v>1407.78</v>
+        <v>1835.25</v>
       </c>
       <c r="L5" t="n" s="0">
-        <v>1411.15</v>
+        <v>1314.03</v>
       </c>
       <c r="M5" t="n" s="0">
-        <v>1594.85</v>
+        <v>1931.49</v>
       </c>
       <c r="N5" t="n" s="0">
-        <v>1820.1</v>
+        <v>1657.84</v>
       </c>
       <c r="O5" t="n" s="0">
-        <v>1271.39</v>
+        <v>1871.97</v>
       </c>
     </row>
     <row r="6">
@@ -500,40 +500,40 @@
         <v>24</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>1699.25</v>
+        <v>1893.6</v>
       </c>
       <c r="E6" t="n" s="0">
-        <v>1404.86</v>
+        <v>1989.77</v>
       </c>
       <c r="F6" t="n" s="0">
-        <v>1211.64</v>
+        <v>1243.36</v>
       </c>
       <c r="G6" t="n" s="0">
-        <v>1700.0</v>
+        <v>1494.39</v>
       </c>
       <c r="H6" t="n" s="0">
-        <v>1408.16</v>
+        <v>1327.22</v>
       </c>
       <c r="I6" t="n" s="0">
-        <v>1531.24</v>
+        <v>1415.77</v>
       </c>
       <c r="J6" t="n" s="0">
-        <v>1350.26</v>
+        <v>1800.24</v>
       </c>
       <c r="K6" t="n" s="0">
-        <v>1978.67</v>
+        <v>1750.57</v>
       </c>
       <c r="L6" t="n" s="0">
-        <v>1395.19</v>
+        <v>1674.9</v>
       </c>
       <c r="M6" t="n" s="0">
-        <v>1673.83</v>
+        <v>1406.45</v>
       </c>
       <c r="N6" t="n" s="0">
-        <v>1463.25</v>
+        <v>1539.39</v>
       </c>
       <c r="O6" t="n" s="0">
-        <v>1469.5</v>
+        <v>1683.01</v>
       </c>
     </row>
     <row r="7">
@@ -547,40 +547,40 @@
         <v>26</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>1259.13</v>
+        <v>1906.76</v>
       </c>
       <c r="E7" t="n" s="0">
-        <v>1341.86</v>
+        <v>1350.06</v>
       </c>
       <c r="F7" t="n" s="0">
-        <v>1848.62</v>
+        <v>1910.9</v>
       </c>
       <c r="G7" t="n" s="0">
-        <v>1297.55</v>
+        <v>1643.01</v>
       </c>
       <c r="H7" t="n" s="0">
-        <v>1510.85</v>
+        <v>1790.8</v>
       </c>
       <c r="I7" t="n" s="0">
-        <v>1385.29</v>
+        <v>1959.18</v>
       </c>
       <c r="J7" t="n" s="0">
-        <v>1820.84</v>
+        <v>1375.5</v>
       </c>
       <c r="K7" t="n" s="0">
-        <v>1710.4</v>
+        <v>1491.52</v>
       </c>
       <c r="L7" t="n" s="0">
-        <v>1905.91</v>
+        <v>1811.7</v>
       </c>
       <c r="M7" t="n" s="0">
-        <v>1438.77</v>
+        <v>1371.4</v>
       </c>
       <c r="N7" t="n" s="0">
-        <v>1612.84</v>
+        <v>1389.94</v>
       </c>
       <c r="O7" t="n" s="0">
-        <v>1687.97</v>
+        <v>1915.96</v>
       </c>
     </row>
     <row r="8">
@@ -594,40 +594,40 @@
         <v>28</v>
       </c>
       <c r="D8" t="n" s="0">
-        <v>1983.88</v>
+        <v>1461.83</v>
       </c>
       <c r="E8" t="n" s="0">
-        <v>1980.6</v>
+        <v>1209.77</v>
       </c>
       <c r="F8" t="n" s="0">
-        <v>1645.17</v>
+        <v>1651.23</v>
       </c>
       <c r="G8" t="n" s="0">
-        <v>1536.93</v>
+        <v>1924.34</v>
       </c>
       <c r="H8" t="n" s="0">
-        <v>1548.1</v>
+        <v>1208.95</v>
       </c>
       <c r="I8" t="n" s="0">
-        <v>1778.58</v>
+        <v>1539.76</v>
       </c>
       <c r="J8" t="n" s="0">
-        <v>1474.47</v>
+        <v>1420.07</v>
       </c>
       <c r="K8" t="n" s="0">
-        <v>1785.51</v>
+        <v>1635.06</v>
       </c>
       <c r="L8" t="n" s="0">
-        <v>1932.48</v>
+        <v>1433.5</v>
       </c>
       <c r="M8" t="n" s="0">
-        <v>1589.19</v>
+        <v>1229.1</v>
       </c>
       <c r="N8" t="n" s="0">
-        <v>1458.79</v>
+        <v>1744.92</v>
       </c>
       <c r="O8" t="n" s="0">
-        <v>1901.86</v>
+        <v>1962.78</v>
       </c>
     </row>
     <row r="9">
@@ -641,40 +641,40 @@
         <v>30</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>1840.26</v>
+        <v>1441.47</v>
       </c>
       <c r="E9" t="n" s="0">
-        <v>1496.07</v>
+        <v>1411.17</v>
       </c>
       <c r="F9" t="n" s="0">
-        <v>1928.39</v>
+        <v>1233.76</v>
       </c>
       <c r="G9" t="n" s="0">
-        <v>1391.09</v>
+        <v>1707.83</v>
       </c>
       <c r="H9" t="n" s="0">
-        <v>1903.11</v>
+        <v>1297.25</v>
       </c>
       <c r="I9" t="n" s="0">
-        <v>1818.24</v>
+        <v>1772.39</v>
       </c>
       <c r="J9" t="n" s="0">
-        <v>1426.23</v>
+        <v>1271.42</v>
       </c>
       <c r="K9" t="n" s="0">
-        <v>1683.15</v>
+        <v>1488.64</v>
       </c>
       <c r="L9" t="n" s="0">
-        <v>1497.03</v>
+        <v>1884.07</v>
       </c>
       <c r="M9" t="n" s="0">
-        <v>1288.21</v>
+        <v>1428.45</v>
       </c>
       <c r="N9" t="n" s="0">
-        <v>1383.27</v>
+        <v>1256.17</v>
       </c>
       <c r="O9" t="n" s="0">
-        <v>1505.55</v>
+        <v>1713.68</v>
       </c>
     </row>
     <row r="10">
@@ -688,40 +688,40 @@
         <v>32</v>
       </c>
       <c r="D10" t="n" s="0">
-        <v>1764.97</v>
+        <v>1888.02</v>
       </c>
       <c r="E10" t="n" s="0">
-        <v>1594.33</v>
+        <v>1823.68</v>
       </c>
       <c r="F10" t="n" s="0">
-        <v>1419.36</v>
+        <v>1729.87</v>
       </c>
       <c r="G10" t="n" s="0">
-        <v>1542.34</v>
+        <v>1971.46</v>
       </c>
       <c r="H10" t="n" s="0">
-        <v>1834.18</v>
+        <v>1914.79</v>
       </c>
       <c r="I10" t="n" s="0">
-        <v>1601.74</v>
+        <v>1582.71</v>
       </c>
       <c r="J10" t="n" s="0">
-        <v>1311.4</v>
+        <v>1602.14</v>
       </c>
       <c r="K10" t="n" s="0">
-        <v>1312.41</v>
+        <v>1424.19</v>
       </c>
       <c r="L10" t="n" s="0">
-        <v>1279.72</v>
+        <v>1686.59</v>
       </c>
       <c r="M10" t="n" s="0">
-        <v>1610.25</v>
+        <v>1362.62</v>
       </c>
       <c r="N10" t="n" s="0">
-        <v>1346.14</v>
+        <v>1419.33</v>
       </c>
       <c r="O10" t="n" s="0">
-        <v>1557.44</v>
+        <v>1622.64</v>
       </c>
     </row>
     <row r="11">
@@ -735,40 +735,40 @@
         <v>34</v>
       </c>
       <c r="D11" t="n" s="0">
-        <v>1773.86</v>
+        <v>1830.16</v>
       </c>
       <c r="E11" t="n" s="0">
-        <v>1877.51</v>
+        <v>1298.76</v>
       </c>
       <c r="F11" t="n" s="0">
-        <v>1875.85</v>
+        <v>1405.17</v>
       </c>
       <c r="G11" t="n" s="0">
-        <v>1411.8</v>
+        <v>1416.85</v>
       </c>
       <c r="H11" t="n" s="0">
-        <v>1774.22</v>
+        <v>1954.73</v>
       </c>
       <c r="I11" t="n" s="0">
-        <v>1530.07</v>
+        <v>1806.71</v>
       </c>
       <c r="J11" t="n" s="0">
-        <v>1420.77</v>
+        <v>1200.67</v>
       </c>
       <c r="K11" t="n" s="0">
-        <v>1233.67</v>
+        <v>1919.49</v>
       </c>
       <c r="L11" t="n" s="0">
-        <v>1641.98</v>
+        <v>1532.37</v>
       </c>
       <c r="M11" t="n" s="0">
-        <v>1504.52</v>
+        <v>1497.43</v>
       </c>
       <c r="N11" t="n" s="0">
-        <v>1413.16</v>
+        <v>1456.6</v>
       </c>
       <c r="O11" t="n" s="0">
-        <v>1208.77</v>
+        <v>1385.27</v>
       </c>
     </row>
     <row r="12">
@@ -782,40 +782,40 @@
         <v>36</v>
       </c>
       <c r="D12" t="n" s="0">
-        <v>1944.63</v>
+        <v>1931.37</v>
       </c>
       <c r="E12" t="n" s="0">
-        <v>1905.55</v>
+        <v>1382.13</v>
       </c>
       <c r="F12" t="n" s="0">
-        <v>1453.45</v>
+        <v>1282.66</v>
       </c>
       <c r="G12" t="n" s="0">
-        <v>1895.11</v>
+        <v>1802.47</v>
       </c>
       <c r="H12" t="n" s="0">
-        <v>1686.03</v>
+        <v>1616.42</v>
       </c>
       <c r="I12" t="n" s="0">
-        <v>1737.01</v>
+        <v>1988.14</v>
       </c>
       <c r="J12" t="n" s="0">
-        <v>1349.73</v>
+        <v>1633.24</v>
       </c>
       <c r="K12" t="n" s="0">
-        <v>1759.06</v>
+        <v>1349.1</v>
       </c>
       <c r="L12" t="n" s="0">
-        <v>1819.95</v>
+        <v>1617.87</v>
       </c>
       <c r="M12" t="n" s="0">
-        <v>1357.08</v>
+        <v>1876.2</v>
       </c>
       <c r="N12" t="n" s="0">
-        <v>1637.85</v>
+        <v>1410.51</v>
       </c>
       <c r="O12" t="n" s="0">
-        <v>1260.37</v>
+        <v>1648.56</v>
       </c>
     </row>
     <row r="13">
@@ -829,40 +829,40 @@
         <v>38</v>
       </c>
       <c r="D13" t="n" s="0">
-        <v>1441.35</v>
+        <v>1285.52</v>
       </c>
       <c r="E13" t="n" s="0">
-        <v>1627.54</v>
+        <v>1944.6</v>
       </c>
       <c r="F13" t="n" s="0">
-        <v>1529.84</v>
+        <v>1591.29</v>
       </c>
       <c r="G13" t="n" s="0">
-        <v>1575.42</v>
+        <v>1566.71</v>
       </c>
       <c r="H13" t="n" s="0">
-        <v>1913.09</v>
+        <v>1880.55</v>
       </c>
       <c r="I13" t="n" s="0">
-        <v>1372.27</v>
+        <v>1824.68</v>
       </c>
       <c r="J13" t="n" s="0">
-        <v>1914.38</v>
+        <v>1834.87</v>
       </c>
       <c r="K13" t="n" s="0">
-        <v>1405.4</v>
+        <v>1724.01</v>
       </c>
       <c r="L13" t="n" s="0">
-        <v>1474.02</v>
+        <v>1322.8</v>
       </c>
       <c r="M13" t="n" s="0">
-        <v>1229.29</v>
+        <v>1817.01</v>
       </c>
       <c r="N13" t="n" s="0">
-        <v>1533.74</v>
+        <v>1404.97</v>
       </c>
       <c r="O13" t="n" s="0">
-        <v>1897.75</v>
+        <v>1953.8</v>
       </c>
     </row>
     <row r="14">
@@ -876,40 +876,40 @@
         <v>40</v>
       </c>
       <c r="D14" t="n" s="0">
-        <v>1587.59</v>
+        <v>1398.53</v>
       </c>
       <c r="E14" t="n" s="0">
-        <v>1675.22</v>
+        <v>1787.05</v>
       </c>
       <c r="F14" t="n" s="0">
-        <v>1987.44</v>
+        <v>1839.5</v>
       </c>
       <c r="G14" t="n" s="0">
-        <v>1916.65</v>
+        <v>1619.55</v>
       </c>
       <c r="H14" t="n" s="0">
-        <v>1228.49</v>
+        <v>1347.35</v>
       </c>
       <c r="I14" t="n" s="0">
-        <v>1520.68</v>
+        <v>1233.6</v>
       </c>
       <c r="J14" t="n" s="0">
-        <v>1363.61</v>
+        <v>1427.79</v>
       </c>
       <c r="K14" t="n" s="0">
-        <v>1329.98</v>
+        <v>1210.99</v>
       </c>
       <c r="L14" t="n" s="0">
-        <v>1668.17</v>
+        <v>1385.1</v>
       </c>
       <c r="M14" t="n" s="0">
-        <v>1319.7</v>
+        <v>1962.78</v>
       </c>
       <c r="N14" t="n" s="0">
-        <v>1874.76</v>
+        <v>1605.7</v>
       </c>
       <c r="O14" t="n" s="0">
-        <v>1437.53</v>
+        <v>1771.21</v>
       </c>
     </row>
     <row r="15">
@@ -923,40 +923,40 @@
         <v>42</v>
       </c>
       <c r="D15" t="n" s="0">
-        <v>1308.07</v>
+        <v>1582.89</v>
       </c>
       <c r="E15" t="n" s="0">
-        <v>1905.42</v>
+        <v>1245.01</v>
       </c>
       <c r="F15" t="n" s="0">
-        <v>1475.72</v>
+        <v>1654.66</v>
       </c>
       <c r="G15" t="n" s="0">
-        <v>1546.99</v>
+        <v>1663.61</v>
       </c>
       <c r="H15" t="n" s="0">
-        <v>1323.2</v>
+        <v>1210.68</v>
       </c>
       <c r="I15" t="n" s="0">
-        <v>1659.41</v>
+        <v>1401.87</v>
       </c>
       <c r="J15" t="n" s="0">
-        <v>1466.88</v>
+        <v>1391.67</v>
       </c>
       <c r="K15" t="n" s="0">
-        <v>1411.52</v>
+        <v>1969.86</v>
       </c>
       <c r="L15" t="n" s="0">
-        <v>1916.38</v>
+        <v>1967.12</v>
       </c>
       <c r="M15" t="n" s="0">
-        <v>1941.08</v>
+        <v>1864.22</v>
       </c>
       <c r="N15" t="n" s="0">
-        <v>1536.92</v>
+        <v>1862.97</v>
       </c>
       <c r="O15" t="n" s="0">
-        <v>1974.6</v>
+        <v>1216.81</v>
       </c>
     </row>
     <row r="16">
@@ -970,40 +970,40 @@
         <v>44</v>
       </c>
       <c r="D16" t="n" s="0">
-        <v>1847.23</v>
+        <v>1855.57</v>
       </c>
       <c r="E16" t="n" s="0">
-        <v>1948.23</v>
+        <v>1862.61</v>
       </c>
       <c r="F16" t="n" s="0">
-        <v>1775.06</v>
+        <v>1804.82</v>
       </c>
       <c r="G16" t="n" s="0">
-        <v>1224.85</v>
+        <v>1562.6</v>
       </c>
       <c r="H16" t="n" s="0">
-        <v>1387.98</v>
+        <v>1229.78</v>
       </c>
       <c r="I16" t="n" s="0">
-        <v>1349.49</v>
+        <v>1255.45</v>
       </c>
       <c r="J16" t="n" s="0">
-        <v>1483.37</v>
+        <v>1610.74</v>
       </c>
       <c r="K16" t="n" s="0">
-        <v>1545.77</v>
+        <v>1228.98</v>
       </c>
       <c r="L16" t="n" s="0">
-        <v>1371.64</v>
+        <v>1520.44</v>
       </c>
       <c r="M16" t="n" s="0">
-        <v>1723.82</v>
+        <v>1969.89</v>
       </c>
       <c r="N16" t="n" s="0">
-        <v>1945.59</v>
+        <v>1945.27</v>
       </c>
       <c r="O16" t="n" s="0">
-        <v>1352.01</v>
+        <v>1449.08</v>
       </c>
     </row>
     <row r="17">
@@ -1017,40 +1017,40 @@
         <v>46</v>
       </c>
       <c r="D17" t="n" s="0">
-        <v>1336.15</v>
+        <v>1967.76</v>
       </c>
       <c r="E17" t="n" s="0">
-        <v>1361.74</v>
+        <v>1525.11</v>
       </c>
       <c r="F17" t="n" s="0">
-        <v>1459.94</v>
+        <v>1770.0</v>
       </c>
       <c r="G17" t="n" s="0">
-        <v>1836.2</v>
+        <v>1706.79</v>
       </c>
       <c r="H17" t="n" s="0">
-        <v>1531.66</v>
+        <v>1522.94</v>
       </c>
       <c r="I17" t="n" s="0">
-        <v>1927.56</v>
+        <v>1926.98</v>
       </c>
       <c r="J17" t="n" s="0">
-        <v>1518.64</v>
+        <v>1998.62</v>
       </c>
       <c r="K17" t="n" s="0">
-        <v>1707.15</v>
+        <v>1775.97</v>
       </c>
       <c r="L17" t="n" s="0">
-        <v>1946.1</v>
+        <v>1545.13</v>
       </c>
       <c r="M17" t="n" s="0">
-        <v>1851.34</v>
+        <v>1467.77</v>
       </c>
       <c r="N17" t="n" s="0">
-        <v>1418.19</v>
+        <v>1473.4</v>
       </c>
       <c r="O17" t="n" s="0">
-        <v>1282.31</v>
+        <v>1824.83</v>
       </c>
     </row>
     <row r="18">
@@ -1064,40 +1064,40 @@
         <v>48</v>
       </c>
       <c r="D18" t="n" s="0">
-        <v>1717.76</v>
+        <v>1608.35</v>
       </c>
       <c r="E18" t="n" s="0">
-        <v>1714.0</v>
+        <v>1634.05</v>
       </c>
       <c r="F18" t="n" s="0">
-        <v>1609.91</v>
+        <v>1856.08</v>
       </c>
       <c r="G18" t="n" s="0">
-        <v>1804.52</v>
+        <v>1432.62</v>
       </c>
       <c r="H18" t="n" s="0">
-        <v>1541.62</v>
+        <v>1646.47</v>
       </c>
       <c r="I18" t="n" s="0">
-        <v>1708.27</v>
+        <v>1620.44</v>
       </c>
       <c r="J18" t="n" s="0">
-        <v>1351.08</v>
+        <v>1352.46</v>
       </c>
       <c r="K18" t="n" s="0">
-        <v>1584.9</v>
+        <v>1573.11</v>
       </c>
       <c r="L18" t="n" s="0">
-        <v>1539.64</v>
+        <v>1602.46</v>
       </c>
       <c r="M18" t="n" s="0">
-        <v>1702.95</v>
+        <v>1666.48</v>
       </c>
       <c r="N18" t="n" s="0">
-        <v>1293.0</v>
+        <v>1940.14</v>
       </c>
       <c r="O18" t="n" s="0">
-        <v>1531.06</v>
+        <v>1651.08</v>
       </c>
     </row>
     <row r="19">
@@ -1111,40 +1111,40 @@
         <v>50</v>
       </c>
       <c r="D19" t="n" s="0">
-        <v>1953.39</v>
+        <v>1511.36</v>
       </c>
       <c r="E19" t="n" s="0">
-        <v>1307.34</v>
+        <v>1578.24</v>
       </c>
       <c r="F19" t="n" s="0">
-        <v>1742.65</v>
+        <v>1745.2</v>
       </c>
       <c r="G19" t="n" s="0">
-        <v>1201.47</v>
+        <v>1335.35</v>
       </c>
       <c r="H19" t="n" s="0">
-        <v>1930.81</v>
+        <v>1734.85</v>
       </c>
       <c r="I19" t="n" s="0">
-        <v>1427.28</v>
+        <v>1566.13</v>
       </c>
       <c r="J19" t="n" s="0">
-        <v>1660.88</v>
+        <v>1413.88</v>
       </c>
       <c r="K19" t="n" s="0">
-        <v>1534.28</v>
+        <v>1813.57</v>
       </c>
       <c r="L19" t="n" s="0">
-        <v>1416.96</v>
+        <v>1678.44</v>
       </c>
       <c r="M19" t="n" s="0">
-        <v>1323.77</v>
+        <v>1724.53</v>
       </c>
       <c r="N19" t="n" s="0">
-        <v>1610.63</v>
+        <v>1551.61</v>
       </c>
       <c r="O19" t="n" s="0">
-        <v>1430.45</v>
+        <v>1201.43</v>
       </c>
     </row>
     <row r="20">
@@ -1158,40 +1158,40 @@
         <v>52</v>
       </c>
       <c r="D20" t="n" s="0">
-        <v>1922.08</v>
+        <v>1360.65</v>
       </c>
       <c r="E20" t="n" s="0">
-        <v>1329.64</v>
+        <v>1298.68</v>
       </c>
       <c r="F20" t="n" s="0">
-        <v>1444.26</v>
+        <v>1952.05</v>
       </c>
       <c r="G20" t="n" s="0">
-        <v>1628.57</v>
+        <v>1370.57</v>
       </c>
       <c r="H20" t="n" s="0">
-        <v>1728.64</v>
+        <v>1266.9</v>
       </c>
       <c r="I20" t="n" s="0">
-        <v>1949.3</v>
+        <v>1728.7</v>
       </c>
       <c r="J20" t="n" s="0">
-        <v>1320.31</v>
+        <v>1214.92</v>
       </c>
       <c r="K20" t="n" s="0">
-        <v>1990.34</v>
+        <v>1216.89</v>
       </c>
       <c r="L20" t="n" s="0">
-        <v>1911.88</v>
+        <v>1608.87</v>
       </c>
       <c r="M20" t="n" s="0">
-        <v>1461.17</v>
+        <v>1530.11</v>
       </c>
       <c r="N20" t="n" s="0">
-        <v>1865.33</v>
+        <v>1452.04</v>
       </c>
       <c r="O20" t="n" s="0">
-        <v>1423.0</v>
+        <v>1972.62</v>
       </c>
     </row>
     <row r="21">
@@ -1205,40 +1205,40 @@
         <v>54</v>
       </c>
       <c r="D21" t="n" s="0">
-        <v>1387.39</v>
+        <v>1623.72</v>
       </c>
       <c r="E21" t="n" s="0">
-        <v>1961.79</v>
+        <v>1964.72</v>
       </c>
       <c r="F21" t="n" s="0">
-        <v>1547.55</v>
+        <v>1506.76</v>
       </c>
       <c r="G21" t="n" s="0">
-        <v>1596.95</v>
+        <v>1572.82</v>
       </c>
       <c r="H21" t="n" s="0">
-        <v>1261.67</v>
+        <v>1685.51</v>
       </c>
       <c r="I21" t="n" s="0">
-        <v>1235.34</v>
+        <v>1775.55</v>
       </c>
       <c r="J21" t="n" s="0">
-        <v>1804.7</v>
+        <v>1462.85</v>
       </c>
       <c r="K21" t="n" s="0">
-        <v>1973.77</v>
+        <v>1718.96</v>
       </c>
       <c r="L21" t="n" s="0">
-        <v>1850.76</v>
+        <v>1364.66</v>
       </c>
       <c r="M21" t="n" s="0">
-        <v>1301.56</v>
+        <v>1403.5</v>
       </c>
       <c r="N21" t="n" s="0">
-        <v>1969.26</v>
+        <v>1994.51</v>
       </c>
       <c r="O21" t="n" s="0">
-        <v>1641.92</v>
+        <v>1939.04</v>
       </c>
     </row>
     <row r="22">
@@ -1252,40 +1252,40 @@
         <v>56</v>
       </c>
       <c r="D22" t="n" s="0">
-        <v>1444.53</v>
+        <v>1959.51</v>
       </c>
       <c r="E22" t="n" s="0">
-        <v>1590.0</v>
+        <v>1273.55</v>
       </c>
       <c r="F22" t="n" s="0">
-        <v>1359.93</v>
+        <v>1910.25</v>
       </c>
       <c r="G22" t="n" s="0">
-        <v>1864.54</v>
+        <v>1626.15</v>
       </c>
       <c r="H22" t="n" s="0">
-        <v>1433.14</v>
+        <v>1637.22</v>
       </c>
       <c r="I22" t="n" s="0">
-        <v>1407.5</v>
+        <v>1732.34</v>
       </c>
       <c r="J22" t="n" s="0">
-        <v>1859.38</v>
+        <v>1668.76</v>
       </c>
       <c r="K22" t="n" s="0">
-        <v>1675.53</v>
+        <v>1743.91</v>
       </c>
       <c r="L22" t="n" s="0">
-        <v>1375.03</v>
+        <v>1559.71</v>
       </c>
       <c r="M22" t="n" s="0">
-        <v>1510.91</v>
+        <v>1238.9</v>
       </c>
       <c r="N22" t="n" s="0">
-        <v>1673.47</v>
+        <v>1696.14</v>
       </c>
       <c r="O22" t="n" s="0">
-        <v>1317.54</v>
+        <v>1419.78</v>
       </c>
     </row>
     <row r="23">
@@ -1299,40 +1299,40 @@
         <v>58</v>
       </c>
       <c r="D23" t="n" s="0">
-        <v>1974.29</v>
+        <v>1433.57</v>
       </c>
       <c r="E23" t="n" s="0">
-        <v>1766.16</v>
+        <v>1254.47</v>
       </c>
       <c r="F23" t="n" s="0">
-        <v>1768.51</v>
+        <v>1209.15</v>
       </c>
       <c r="G23" t="n" s="0">
-        <v>1996.98</v>
+        <v>1803.75</v>
       </c>
       <c r="H23" t="n" s="0">
-        <v>1348.52</v>
+        <v>1610.89</v>
       </c>
       <c r="I23" t="n" s="0">
-        <v>1869.62</v>
+        <v>1747.18</v>
       </c>
       <c r="J23" t="n" s="0">
-        <v>1908.49</v>
+        <v>1550.37</v>
       </c>
       <c r="K23" t="n" s="0">
-        <v>1738.8</v>
+        <v>1952.41</v>
       </c>
       <c r="L23" t="n" s="0">
-        <v>1606.45</v>
+        <v>1381.78</v>
       </c>
       <c r="M23" t="n" s="0">
-        <v>1726.89</v>
+        <v>1521.8</v>
       </c>
       <c r="N23" t="n" s="0">
-        <v>1665.28</v>
+        <v>1766.64</v>
       </c>
       <c r="O23" t="n" s="0">
-        <v>1655.3</v>
+        <v>1505.06</v>
       </c>
     </row>
     <row r="24">
@@ -1346,40 +1346,40 @@
         <v>60</v>
       </c>
       <c r="D24" t="n" s="0">
-        <v>1818.02</v>
+        <v>1437.05</v>
       </c>
       <c r="E24" t="n" s="0">
-        <v>1729.13</v>
+        <v>1904.06</v>
       </c>
       <c r="F24" t="n" s="0">
-        <v>1650.38</v>
+        <v>1713.02</v>
       </c>
       <c r="G24" t="n" s="0">
-        <v>1900.53</v>
+        <v>1350.83</v>
       </c>
       <c r="H24" t="n" s="0">
-        <v>1547.94</v>
+        <v>1843.22</v>
       </c>
       <c r="I24" t="n" s="0">
-        <v>1636.14</v>
+        <v>1854.12</v>
       </c>
       <c r="J24" t="n" s="0">
-        <v>1517.65</v>
+        <v>1740.4</v>
       </c>
       <c r="K24" t="n" s="0">
-        <v>1963.95</v>
+        <v>1942.64</v>
       </c>
       <c r="L24" t="n" s="0">
-        <v>1836.69</v>
+        <v>1660.09</v>
       </c>
       <c r="M24" t="n" s="0">
-        <v>1270.2</v>
+        <v>1752.6</v>
       </c>
       <c r="N24" t="n" s="0">
-        <v>1212.32</v>
+        <v>1625.39</v>
       </c>
       <c r="O24" t="n" s="0">
-        <v>1763.71</v>
+        <v>1795.86</v>
       </c>
     </row>
     <row r="25">
@@ -1393,40 +1393,40 @@
         <v>62</v>
       </c>
       <c r="D25" t="n" s="0">
-        <v>1451.67</v>
+        <v>1344.46</v>
       </c>
       <c r="E25" t="n" s="0">
-        <v>1544.13</v>
+        <v>1897.76</v>
       </c>
       <c r="F25" t="n" s="0">
-        <v>1692.18</v>
+        <v>1227.34</v>
       </c>
       <c r="G25" t="n" s="0">
-        <v>1832.3</v>
+        <v>1616.75</v>
       </c>
       <c r="H25" t="n" s="0">
-        <v>1394.18</v>
+        <v>1921.92</v>
       </c>
       <c r="I25" t="n" s="0">
-        <v>1691.58</v>
+        <v>1371.56</v>
       </c>
       <c r="J25" t="n" s="0">
-        <v>1322.85</v>
+        <v>1807.65</v>
       </c>
       <c r="K25" t="n" s="0">
-        <v>1944.2</v>
+        <v>1637.6</v>
       </c>
       <c r="L25" t="n" s="0">
-        <v>1236.3</v>
+        <v>1571.7</v>
       </c>
       <c r="M25" t="n" s="0">
-        <v>1536.95</v>
+        <v>1376.89</v>
       </c>
       <c r="N25" t="n" s="0">
-        <v>1549.52</v>
+        <v>1622.56</v>
       </c>
       <c r="O25" t="n" s="0">
-        <v>1817.04</v>
+        <v>1892.43</v>
       </c>
     </row>
     <row r="26">
@@ -1440,40 +1440,40 @@
         <v>64</v>
       </c>
       <c r="D26" t="n" s="0">
-        <v>1674.9</v>
+        <v>1958.23</v>
       </c>
       <c r="E26" t="n" s="0">
-        <v>1437.23</v>
+        <v>1618.0</v>
       </c>
       <c r="F26" t="n" s="0">
-        <v>1473.72</v>
+        <v>1901.51</v>
       </c>
       <c r="G26" t="n" s="0">
-        <v>1425.28</v>
+        <v>1349.6</v>
       </c>
       <c r="H26" t="n" s="0">
-        <v>1928.58</v>
+        <v>1355.86</v>
       </c>
       <c r="I26" t="n" s="0">
-        <v>1547.13</v>
+        <v>1590.53</v>
       </c>
       <c r="J26" t="n" s="0">
-        <v>1214.07</v>
+        <v>1648.63</v>
       </c>
       <c r="K26" t="n" s="0">
-        <v>1996.71</v>
+        <v>1224.08</v>
       </c>
       <c r="L26" t="n" s="0">
-        <v>1466.26</v>
+        <v>1351.96</v>
       </c>
       <c r="M26" t="n" s="0">
-        <v>1903.68</v>
+        <v>1567.03</v>
       </c>
       <c r="N26" t="n" s="0">
-        <v>1205.99</v>
+        <v>1855.84</v>
       </c>
       <c r="O26" t="n" s="0">
-        <v>1919.94</v>
+        <v>1624.7</v>
       </c>
     </row>
   </sheetData>
